--- a/etf_holdings/2026-10-10_common_holdings_all.xlsx
+++ b/etf_holdings/2026-10-10_common_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP5"/>
+  <dimension ref="A1:AP4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,12 +1003,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1016,357 +1016,171 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.19%</t>
+          <t>7.16%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5086000</v>
+        <v>6062000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.31%</t>
+          <t>5.51%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1050000</v>
+        <v>1250000</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>5.89%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>249000</v>
+        <v>134000</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6.80%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>736000</v>
+        <v>372000</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>6.37%</t>
+          <t>5.03%</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1950000</v>
+        <v>2100000</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>143000</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>6.90%</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>871000</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>1.46%</t>
         </is>
       </c>
-      <c r="U4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="X4" t="n">
-        <v>179000</v>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2.08%</t>
-        </is>
-      </c>
       <c r="AA4" t="n">
-        <v>165000</v>
+        <v>158000</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5.57%</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>294000</v>
+        <v>278000</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>269000</v>
+        <v>375000</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>5.96%</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>34000</v>
+        <v>176000</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>6.34%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>413000</v>
+        <v>377000</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>57.98%</t>
+          <t>53.63%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>4.83%</t>
+          <t>4.47%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
-        <is>
-          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A,00400A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6062000</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>5.51%</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2.32%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>134000</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2.52%</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>372000</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>5.03%</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>3.07%</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>143000</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>6.90%</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
-        <v>871000</v>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1.46%</t>
-        </is>
-      </c>
-      <c r="AA5" t="n">
-        <v>158000</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>3.86%</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>278000</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>5.59%</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>375000</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>5.96%</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>176000</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>4.25%</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>377000</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>53.63%</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>4.47%</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
         <is>
           <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A,00400A</t>
         </is>
